--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_255_R26.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_255_R26.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2603</v>
+        <v>4.5266</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3017</v>
+        <v>1.2884</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0414</v>
+        <v>3.2383</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1737</v>
+        <v>1.8268</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7825</v>
+        <v>0.9268</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6089</v>
+        <v>0.9</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8715</v>
+        <v>0.8014</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6875</v>
+        <v>1.1595</v>
       </c>
       <c r="L2" t="n">
-        <v>0.184</v>
+        <v>-0.3581</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.6978</v>
+        <v>1.0254</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9049</v>
+        <v>-0.2327</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7929</v>
+        <v>1.2582</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3195</v>
+        <v>0.9278</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9811</v>
+        <v>0.6998</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6621</v>
+        <v>0.4327</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3189</v>
+        <v>0.2671</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8189</v>
+        <v>3.443</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5806</v>
+        <v>4.248</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2383</v>
+        <v>-0.805</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8268</v>
+        <v>1.2585</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9268</v>
+        <v>-2.5223</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9</v>
+        <v>3.7809</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8014</v>
+        <v>3.2821</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1595</v>
+        <v>-0.9236</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3581</v>
+        <v>4.2057</v>
       </c>
       <c r="M3" t="n">
-        <v>1.0254</v>
+        <v>-2.0235</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2327</v>
+        <v>-1.5987</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2582</v>
+        <v>-0.4248</v>
       </c>
       <c r="P3" t="n">
         <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.275</v>
+        <v>-0.0703</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2671</v>
+        <v>-0.0288</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0722</v>
+        <v>1.3558</v>
       </c>
       <c r="W3" t="n">
-        <v>1.214</v>
+        <v>2.428</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5772</v>
+        <v>2.9038</v>
       </c>
       <c r="E4" t="n">
-        <v>2.815</v>
+        <v>2.3432</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7622</v>
+        <v>0.5606</v>
       </c>
       <c r="G4" t="n">
         <v>0.2008</v>
@@ -766,13 +766,13 @@
         <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>1.057</v>
+        <v>0.3835</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3189</v>
+        <v>-0.1529</v>
       </c>
       <c r="U4" t="n">
-        <v>0.738</v>
+        <v>0.5364</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2078</v>
+        <v>2.7104</v>
       </c>
       <c r="E5" t="n">
-        <v>4.248</v>
+        <v>2.8863</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0402</v>
+        <v>-0.1758</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2585</v>
+        <v>0.1737</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.5223</v>
+        <v>0.7825</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7809</v>
+        <v>-0.6089</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2821</v>
+        <v>1.8715</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.9236</v>
+        <v>1.6875</v>
       </c>
       <c r="L5" t="n">
-        <v>4.2057</v>
+        <v>0.184</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0235</v>
+        <v>-1.6978</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5987</v>
+        <v>-0.9049</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4248</v>
+        <v>-0.7929</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9278</v>
+        <v>2.3195</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3195</v>
+        <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3343</v>
+        <v>1.4312</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0703</v>
+        <v>1.2467</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.264</v>
+        <v>0.1845</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3558</v>
+        <v>-1.214</v>
       </c>
       <c r="W5" t="n">
-        <v>2.428</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6178</v>
+        <v>-0.5505</v>
       </c>
       <c r="E6" t="n">
         <v>0.0287</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6465</v>
+        <v>-0.5793</v>
       </c>
       <c r="G6" t="n">
         <v>-1.0597</v>
@@ -922,13 +922,13 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2539</v>
+        <v>-0.1867</v>
       </c>
       <c r="T6" t="n">
         <v>-0.2161</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0378</v>
+        <v>0.0294</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2329</v>
+        <v>-1.3001</v>
       </c>
       <c r="E7" t="n">
         <v>0.9891</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.222</v>
+        <v>-2.2892</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8117</v>
@@ -1000,13 +1000,13 @@
         <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0448</v>
+        <v>-0.112</v>
       </c>
       <c r="T7" t="n">
         <v>-0.2082</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1634</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>-1.0722</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9568</v>
+        <v>-1.5865</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9833</v>
+        <v>-2.7474</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0266</v>
+        <v>1.161</v>
       </c>
       <c r="G8" t="n">
         <v>-2.4747</v>
@@ -1078,13 +1078,13 @@
         <v>2.5515</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7345</v>
+        <v>1.1048</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5939</v>
+        <v>0.8298</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1406</v>
+        <v>0.275</v>
       </c>
       <c r="V8" t="n">
         <v>-1.6083</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9545</v>
+        <v>-2.9209</v>
       </c>
       <c r="E10" t="n">
         <v>-1.0536</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9008</v>
+        <v>-1.8672</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8354</v>
@@ -1234,13 +1234,13 @@
         <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1191</v>
+        <v>-0.0854</v>
       </c>
       <c r="T10" t="n">
         <v>-0.1415</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.5698</v>
+        <v>-4.8964</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5476</v>
+        <v>-3.0758</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0223</v>
+        <v>-1.8206</v>
       </c>
       <c r="G11" t="n">
         <v>-5.133</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0605</v>
+        <v>-0.387</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1123</v>
+        <v>-0.6405</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0518</v>
+        <v>0.2535</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5361</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5904</v>
+        <v>-5.3874</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.9843</v>
+        <v>-5.5125</v>
       </c>
       <c r="F12" t="n">
-        <v>0.394</v>
+        <v>0.1251</v>
       </c>
       <c r="G12" t="n">
         <v>-7.7644</v>
@@ -1390,13 +1390,13 @@
         <v>2.3195</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7644</v>
+        <v>0.9673</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1617</v>
+        <v>0.6335</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6027</v>
+        <v>0.3339</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6778999999999999</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.289999999999999</v>
+        <v>-5.29</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.765499999999999</v>
+        <v>-1.7654</v>
       </c>
       <c r="F13" t="n">
         <v>-3.5243</v>
@@ -1468,13 +1468,13 @@
         <v>17.3966</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7165</v>
+        <v>3.7164</v>
       </c>
       <c r="T13" t="n">
         <v>1.7132</v>
       </c>
       <c r="U13" t="n">
-        <v>2.0031</v>
+        <v>2.0032</v>
       </c>
       <c r="V13" t="n">
         <v>-4.8249</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.4389</v>
+        <v>6.8264</v>
       </c>
       <c r="E14" t="n">
-        <v>6.8559</v>
+        <v>6.2662</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.417</v>
+        <v>0.5602</v>
       </c>
       <c r="G14" t="n">
         <v>5.7803</v>
@@ -1546,13 +1546,13 @@
         <v>0.6959</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0013</v>
+        <v>0.3861</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9006</v>
+        <v>0.3108</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9019</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>1.3558</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.4244</v>
+        <v>4.7751</v>
       </c>
       <c r="E15" t="n">
         <v>2.2489</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1755</v>
+        <v>2.5262</v>
       </c>
       <c r="G15" t="n">
         <v>3.2788</v>
@@ -1624,13 +1624,13 @@
         <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7512</v>
+        <v>0.1019</v>
       </c>
       <c r="T15" t="n">
         <v>-0.5975</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3487</v>
+        <v>0.6994</v>
       </c>
       <c r="V15" t="n">
         <v>0.9304</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.9054</v>
+        <v>4.6232</v>
       </c>
       <c r="E16" t="n">
         <v>2.2378</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6677</v>
+        <v>2.3855</v>
       </c>
       <c r="G16" t="n">
         <v>4.2396</v>
@@ -1702,13 +1702,13 @@
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6589</v>
+        <v>0.0589</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1019</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5570000000000001</v>
+        <v>0.1608</v>
       </c>
       <c r="V16" t="n">
         <v>0.7886</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3783</v>
+        <v>2.7772</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0582</v>
+        <v>3.1762</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.68</v>
+        <v>-0.399</v>
       </c>
       <c r="G17" t="n">
         <v>1.1873</v>
@@ -1780,13 +1780,13 @@
         <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0286</v>
+        <v>0.4274</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2526</v>
+        <v>0.5335</v>
       </c>
       <c r="V17" t="n">
         <v>0.9304</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3467</v>
+        <v>-0.1279</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1815</v>
+        <v>-0.0636</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1651</v>
+        <v>-0.0643</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1819</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0672</v>
+        <v>0.286</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0672</v>
+        <v>0.168</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. HORTON TUCKER</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6835</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3748</v>
+        <v>-2.0727</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6913</v>
+        <v>1.542</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7459</v>
+        <v>1.8036</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0743</v>
+        <v>0.7863</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3284</v>
+        <v>1.0172</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2993</v>
+        <v>1.0034</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8352</v>
+        <v>0.612</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.5359</v>
+        <v>0.3914</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4466</v>
+        <v>0.8002</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2391</v>
+        <v>0.1744</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2075</v>
+        <v>0.6258</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.2473</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.7112</v>
+        <v>-3.4793</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2544</v>
+        <v>-0.3705</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0351</v>
+        <v>-0.4165</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2192</v>
+        <v>0.0459</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0722</v>
+        <v>0.8197</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>0.8197</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7322</v>
+        <v>-0.6314</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7273</v>
+        <v>-2.2555</v>
       </c>
       <c r="F20" t="n">
-        <v>0.995</v>
+        <v>1.6241</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2931</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9752</v>
+        <v>0.1256</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7389</v>
+        <v>-0.2671</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2363</v>
+        <v>0.3927</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>T. HORTON TUCKER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.844</v>
+        <v>-1.6385</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5445</v>
+        <v>-2.6107</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7005</v>
+        <v>0.9722</v>
       </c>
       <c r="G21" t="n">
-        <v>1.8036</v>
+        <v>0.7459</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7863</v>
+        <v>2.0743</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0172</v>
+        <v>-1.3284</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0034</v>
+        <v>0.2993</v>
       </c>
       <c r="K21" t="n">
-        <v>0.612</v>
+        <v>1.8352</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3914</v>
+        <v>-1.5359</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8002</v>
+        <v>0.4466</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1744</v>
+        <v>0.2391</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6258</v>
+        <v>0.2075</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.7834</v>
+        <v>-3.2473</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4793</v>
+        <v>-3.7112</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6838</v>
+        <v>-0.2093</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8883</v>
+        <v>-0.2711</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7956</v>
+        <v>0.0617</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8197</v>
+        <v>1.0722</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8197</v>
+        <v>1.0722</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. BITIM</t>
+          <t>N. DE COLO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0285</v>
+        <v>-1.7677</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0285</v>
+        <v>-0.0462</v>
       </c>
       <c r="F22" t="n">
-        <v>-0</v>
+        <v>-1.7215</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6172</v>
+        <v>-1.8886</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1358</v>
+        <v>-1.8619</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5185</v>
+        <v>-0.0268</v>
       </c>
       <c r="J22" t="n">
-        <v>0.342</v>
+        <v>0.1341</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9075</v>
+        <v>-1.4719</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5655</v>
+        <v>1.606</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2753</v>
+        <v>-2.0227</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2283</v>
+        <v>-0.39</v>
       </c>
       <c r="O22" t="n">
-        <v>0.047</v>
+        <v>-1.6327</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.0876</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.7834</v>
+        <v>-1.3917</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>0.514</v>
+        <v>-0.4874</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4129</v>
+        <v>-0.3969</v>
       </c>
       <c r="U22" t="n">
-        <v>0.101</v>
+        <v>-0.0905</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0722</v>
+        <v>1.0722</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. COLSON</t>
+          <t>O. BITIM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5731</v>
+        <v>-2.0729</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8556</v>
+        <v>-2.5003</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7174</v>
+        <v>0.4274</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6701</v>
+        <v>0.6172</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2365</v>
+        <v>1.1358</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9067</v>
+        <v>-0.5185</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7522</v>
+        <v>0.342</v>
       </c>
       <c r="K23" t="n">
-        <v>0.605</v>
+        <v>0.9075</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1472</v>
+        <v>-0.5655</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4223</v>
+        <v>0.2753</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3684</v>
+        <v>0.2283</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0539</v>
+        <v>0.047</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6959</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.3917</v>
+        <v>-2.7834</v>
       </c>
       <c r="R23" t="n">
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1349</v>
+        <v>0.4696</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2161</v>
+        <v>-0.0589</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0813</v>
+        <v>0.5285</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N. DE COLO</t>
+          <t>B. COLSON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6492</v>
+        <v>-2.2249</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1641</v>
+        <v>-0.8556</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.485</v>
+        <v>-1.3693</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.8886</v>
+        <v>-0.6701</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8619</v>
+        <v>0.2365</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0268</v>
+        <v>-0.9067</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1341</v>
+        <v>0.7522</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.4719</v>
+        <v>0.605</v>
       </c>
       <c r="L24" t="n">
-        <v>1.606</v>
+        <v>0.1472</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.0227</v>
+        <v>-1.4223</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.39</v>
+        <v>-0.3684</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.6327</v>
+        <v>-1.0539</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3689</v>
+        <v>0.2133</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5149</v>
+        <v>-0.2161</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.854</v>
+        <v>0.4294</v>
       </c>
       <c r="V24" t="n">
-        <v>1.0722</v>
+        <v>-1.0722</v>
       </c>
       <c r="W24" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.289799999999996</v>
+        <v>10.0079</v>
       </c>
       <c r="E25" t="n">
-        <v>3.524499999999999</v>
+        <v>3.5245</v>
       </c>
       <c r="F25" t="n">
-        <v>1.765500000000001</v>
+        <v>6.483499999999998</v>
       </c>
       <c r="G25" t="n">
         <v>14.619</v>
@@ -2389,10 +2389,10 @@
         <v>0.4458000000000002</v>
       </c>
       <c r="N25" t="n">
-        <v>0.4946999999999998</v>
+        <v>0.4947</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.04899999999999971</v>
+        <v>-0.04899999999999993</v>
       </c>
       <c r="P25" t="n">
         <v>-10.4379</v>
@@ -2404,13 +2404,13 @@
         <v>6.9587</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.716399999999999</v>
+        <v>1.0016</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.0032</v>
+        <v>-2.0033</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.7132</v>
+        <v>3.0047</v>
       </c>
       <c r="V25" t="n">
         <v>4.8249</v>
